--- a/交付物/附件2_2026年1-8月投诉去重建议清单.xlsx
+++ b/交付物/附件2_2026年1-8月投诉去重建议清单.xlsx
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>上海中誉物业管理有限公司</t>
+          <t>上海中誉城市运营服务有限公司</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>上海中誉物业管理有限公司</t>
+          <t>上海中誉城市运营服务有限公司</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>上海中誉物业管理有限公司</t>
+          <t>上海中誉城市运营服务有限公司</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
